--- a/salidas/empresas/CCI.xlsx
+++ b/salidas/empresas/CCI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>18.8282642364502</v>
+        <v>18.82826232910156</v>
       </c>
       <c r="C2" t="n">
         <v>31.6299991607666</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.66159248352051</v>
+        <v>18.66159057617188</v>
       </c>
       <c r="C3" t="n">
         <v>31.35000038146973</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.87579154968262</v>
+        <v>16.87578582763672</v>
       </c>
       <c r="C4" t="n">
         <v>28.35000038146973</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>20.03070449829102</v>
+        <v>20.03070259094238</v>
       </c>
       <c r="C5" t="n">
         <v>33.65000152587891</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.45334053039551</v>
+        <v>20.45333480834961</v>
       </c>
       <c r="C9" t="n">
         <v>34.36000061035156</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.97717475891113</v>
+        <v>20.97718048095703</v>
       </c>
       <c r="C10" t="n">
         <v>35.2400016784668</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.03070449829102</v>
+        <v>20.03070259094238</v>
       </c>
       <c r="C11" t="n">
         <v>33.65000152587891</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.51286125183105</v>
+        <v>20.51287078857422</v>
       </c>
       <c r="C12" t="n">
         <v>34.45999908447266</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.22708892822266</v>
+        <v>19.22709083557129</v>
       </c>
       <c r="C13" t="n">
         <v>32.29999923706055</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.92955589294434</v>
+        <v>20.9295539855957</v>
       </c>
       <c r="C14" t="n">
         <v>35.15999984741211</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.12589836120605</v>
+        <v>19.12590217590332</v>
       </c>
       <c r="C16" t="n">
         <v>32.13000106811523</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>20.44143867492676</v>
+        <v>20.44144058227539</v>
       </c>
       <c r="C17" t="n">
         <v>34.34000015258789</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.91769218444824</v>
+        <v>21.91769027709961</v>
       </c>
       <c r="C18" t="n">
         <v>36.81999969482422</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.59030151367188</v>
+        <v>21.59029579162598</v>
       </c>
       <c r="C19" t="n">
         <v>36.27000045776367</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>21.57839965820312</v>
+        <v>21.57839775085449</v>
       </c>
       <c r="C20" t="n">
         <v>36.25</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>24.1856632232666</v>
+        <v>24.1856575012207</v>
       </c>
       <c r="C22" t="n">
         <v>40.63000106811523</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>24.44758033752441</v>
+        <v>24.44757080078125</v>
       </c>
       <c r="C23" t="n">
         <v>41.06999969482422</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>24.7630672454834</v>
+        <v>24.7630615234375</v>
       </c>
       <c r="C25" t="n">
         <v>41.59999847412109</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>21.50101089477539</v>
+        <v>21.50101661682129</v>
       </c>
       <c r="C26" t="n">
         <v>36.11999893188477</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.48315048217773</v>
+        <v>21.48315620422363</v>
       </c>
       <c r="C27" t="n">
         <v>36.09000015258789</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>20.53072929382324</v>
+        <v>20.53072547912598</v>
       </c>
       <c r="C28" t="n">
         <v>34.4900016784668</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.12608528137207</v>
+        <v>23.12608337402344</v>
       </c>
       <c r="C29" t="n">
         <v>38.84999847412109</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>25.29285621643066</v>
+        <v>25.29284477233887</v>
       </c>
       <c r="C30" t="n">
         <v>42.4900016784668</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>23.05465507507324</v>
+        <v>23.05465888977051</v>
       </c>
       <c r="C31" t="n">
         <v>38.72999954223633</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>22.73916435241699</v>
+        <v>22.73916816711426</v>
       </c>
       <c r="C32" t="n">
         <v>38.20000076293945</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.24485778808594</v>
+        <v>17.2448558807373</v>
       </c>
       <c r="C34" t="n">
         <v>28.96999931335449</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.60178279876709</v>
+        <v>12.60177898406982</v>
       </c>
       <c r="C35" t="n">
         <v>21.17000007629395</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.375392913818359</v>
+        <v>8.375394821166992</v>
       </c>
       <c r="C36" t="n">
         <v>14.06999969482422</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.46477794647217</v>
+        <v>10.46477699279785</v>
       </c>
       <c r="C37" t="n">
         <v>17.57999992370605</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.61959266662598</v>
+        <v>11.61959457397461</v>
       </c>
       <c r="C38" t="n">
         <v>19.52000045776367</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.44096660614014</v>
+        <v>10.44096755981445</v>
       </c>
       <c r="C39" t="n">
         <v>17.54000091552734</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.59592437744141</v>
+        <v>14.59591960906982</v>
       </c>
       <c r="C41" t="n">
         <v>24.52000045776367</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.4411563873291</v>
+        <v>14.44115352630615</v>
       </c>
       <c r="C42" t="n">
         <v>24.26000022888184</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.29829502105713</v>
+        <v>14.29829025268555</v>
       </c>
       <c r="C43" t="n">
         <v>24.02000045776367</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.10795021057129</v>
+        <v>17.10794639587402</v>
       </c>
       <c r="C44" t="n">
         <v>28.73999977111816</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.66754341125488</v>
+        <v>18.66754150390625</v>
       </c>
       <c r="C46" t="n">
         <v>31.36000061035156</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.23918533325195</v>
+        <v>23.23918914794922</v>
       </c>
       <c r="C49" t="n">
         <v>39.04000091552734</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.9891242980957</v>
+        <v>21.98911666870117</v>
       </c>
       <c r="C50" t="n">
         <v>36.93999862670898</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.50106430053711</v>
+        <v>22.50105094909668</v>
       </c>
       <c r="C51" t="n">
         <v>37.79999923706055</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.75702285766602</v>
+        <v>22.75702857971191</v>
       </c>
       <c r="C52" t="n">
         <v>38.22999954223633</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.53081512451172</v>
+        <v>22.53081893920898</v>
       </c>
       <c r="C53" t="n">
         <v>37.84999847412109</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.04269790649414</v>
+        <v>22.04270172119141</v>
       </c>
       <c r="C54" t="n">
         <v>37.02999877929688</v>
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.51895713806152</v>
+        <v>23.51896095275879</v>
       </c>
       <c r="C56" t="n">
         <v>39.5099983215332</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>24.47734260559082</v>
+        <v>24.47734451293945</v>
       </c>
       <c r="C57" t="n">
         <v>41.11999893188477</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>26.281005859375</v>
+        <v>26.28099822998047</v>
       </c>
       <c r="C58" t="n">
         <v>44.15000152587891</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>25.66787719726562</v>
+        <v>25.66786766052246</v>
       </c>
       <c r="C59" t="n">
         <v>43.11999893188477</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.72735214233398</v>
+        <v>24.72735023498535</v>
       </c>
       <c r="C60" t="n">
         <v>41.54000091552734</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>26.09050559997559</v>
+        <v>26.09050369262695</v>
       </c>
       <c r="C61" t="n">
         <v>43.83000183105469</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.10237312316895</v>
+        <v>25.10237121582031</v>
       </c>
       <c r="C62" t="n">
         <v>42.16999816894531</v>
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>25.32856369018555</v>
+        <v>25.32857322692871</v>
       </c>
       <c r="C64" t="n">
         <v>42.54999923706055</v>
@@ -1799,11 +1811,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.51310348510742</v>
+        <v>25.51309776306152</v>
       </c>
       <c r="C65" t="n">
         <v>42.86000061035156</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.64996719360352</v>
+        <v>24.64996528625488</v>
       </c>
       <c r="C66" t="n">
         <v>41.40999984741211</v>
@@ -1849,11 +1861,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.28090286254883</v>
+        <v>24.28089714050293</v>
       </c>
       <c r="C67" t="n">
         <v>40.79000091552734</v>
@@ -1874,11 +1886,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>25.83454895019531</v>
+        <v>25.83454132080078</v>
       </c>
       <c r="C68" t="n">
         <v>43.40000152587891</v>
@@ -1899,11 +1911,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>25.85240936279297</v>
+        <v>25.85240364074707</v>
       </c>
       <c r="C69" t="n">
         <v>43.43000030517578</v>
@@ -1924,11 +1936,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.20946502685547</v>
+        <v>24.2094669342041</v>
       </c>
       <c r="C70" t="n">
         <v>40.66999816894531</v>
@@ -1949,11 +1961,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.62020301818848</v>
+        <v>24.62019157409668</v>
       </c>
       <c r="C71" t="n">
         <v>41.36000061035156</v>
@@ -1974,11 +1986,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>25.191650390625</v>
+        <v>25.19165992736816</v>
       </c>
       <c r="C72" t="n">
         <v>42.31999969482422</v>
@@ -1999,11 +2011,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.66791725158691</v>
+        <v>26.66792106628418</v>
       </c>
       <c r="C73" t="n">
         <v>44.79999923706055</v>
@@ -2024,11 +2036,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.85848999023438</v>
+        <v>28.85849952697754</v>
       </c>
       <c r="C74" t="n">
         <v>48.47999954223633</v>
@@ -2049,11 +2061,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.84073257446289</v>
+        <v>30.84072685241699</v>
       </c>
       <c r="C75" t="n">
         <v>51.81000137329102</v>
@@ -2078,11 +2090,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>31.75149345397949</v>
+        <v>31.75149917602539</v>
       </c>
       <c r="C76" t="n">
         <v>53.34000015258789</v>
@@ -2107,11 +2119,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.6980094909668</v>
+        <v>33.69802474975586</v>
       </c>
       <c r="C77" t="n">
         <v>56.61000061035156</v>
@@ -2136,11 +2148,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.50153350830078</v>
+        <v>32.50152587890625</v>
       </c>
       <c r="C78" t="n">
         <v>54.59999847412109</v>
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.91830444335938</v>
+        <v>34.91831207275391</v>
       </c>
       <c r="C79" t="n">
         <v>58.65999984741211</v>
@@ -2194,11 +2206,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>36.8350715637207</v>
+        <v>36.83506393432617</v>
       </c>
       <c r="C80" t="n">
         <v>61.88000106811523</v>
@@ -2223,11 +2235,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>37.77558517456055</v>
+        <v>37.77557754516602</v>
       </c>
       <c r="C81" t="n">
         <v>63.45999908447266</v>
@@ -2252,11 +2264,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>38.15655517578125</v>
+        <v>38.15656280517578</v>
       </c>
       <c r="C82" t="n">
         <v>64.09999847412109</v>
@@ -2281,11 +2293,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>39.73400115966797</v>
+        <v>39.73401260375977</v>
       </c>
       <c r="C83" t="n">
         <v>66.75</v>
@@ -2310,11 +2322,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>40.19235229492188</v>
+        <v>40.19235992431641</v>
       </c>
       <c r="C84" t="n">
         <v>67.51999664306641</v>
@@ -2339,11 +2351,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.95440673828125</v>
+        <v>42.95440292358398</v>
       </c>
       <c r="C85" t="n">
         <v>72.16000366210938</v>
@@ -2368,11 +2380,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.97815704345703</v>
+        <v>41.97814559936523</v>
       </c>
       <c r="C86" t="n">
         <v>70.51999664306641</v>
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.54956817626953</v>
+        <v>41.5495719909668</v>
       </c>
       <c r="C87" t="n">
         <v>69.80000305175781</v>
@@ -2426,11 +2438,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>41.45432662963867</v>
+        <v>41.45433044433594</v>
       </c>
       <c r="C88" t="n">
         <v>69.63999938964844</v>
@@ -2455,11 +2467,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>45.83549118041992</v>
+        <v>45.83548736572266</v>
       </c>
       <c r="C89" t="n">
         <v>77</v>
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>42.4127082824707</v>
+        <v>42.4127197265625</v>
       </c>
       <c r="C90" t="n">
         <v>71.25</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>43.09130096435547</v>
+        <v>43.09131240844727</v>
       </c>
       <c r="C91" t="n">
         <v>72.38999938964844</v>
@@ -2542,11 +2554,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>41.81744766235352</v>
+        <v>41.81743240356445</v>
       </c>
       <c r="C92" t="n">
         <v>70.25</v>
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>41.3233528137207</v>
+        <v>41.3233757019043</v>
       </c>
       <c r="C93" t="n">
         <v>69.41999816894531</v>
@@ -2600,11 +2612,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.47227478027344</v>
+        <v>43.47227096557617</v>
       </c>
       <c r="C94" t="n">
         <v>73.02999877929688</v>
@@ -2629,11 +2641,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>45.25213241577148</v>
+        <v>45.25211334228516</v>
       </c>
       <c r="C95" t="n">
         <v>76.01999664306641</v>
@@ -2658,11 +2670,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>44.18661117553711</v>
+        <v>44.18659210205078</v>
       </c>
       <c r="C96" t="n">
         <v>74.23000335693359</v>
@@ -2687,11 +2699,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>43.71038436889648</v>
+        <v>43.71039581298828</v>
       </c>
       <c r="C97" t="n">
         <v>73.43000030517578</v>
@@ -2716,11 +2728,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.24007797241211</v>
+        <v>42.24006271362305</v>
       </c>
       <c r="C98" t="n">
         <v>70.95999908447266</v>
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>45.18070983886719</v>
+        <v>45.18070602416992</v>
       </c>
       <c r="C99" t="n">
         <v>75.90000152587891</v>
@@ -2774,7 +2786,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>43.49701309204102</v>
+        <v>43.49701690673828</v>
       </c>
       <c r="C101" t="n">
         <v>72.73000335693359</v>
@@ -2832,11 +2844,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>45.88926315307617</v>
+        <v>45.88925552368164</v>
       </c>
       <c r="C102" t="n">
         <v>76.73000335693359</v>
@@ -2861,11 +2873,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>44.62524795532227</v>
+        <v>44.62524032592773</v>
       </c>
       <c r="C103" t="n">
         <v>74.26000213623047</v>
@@ -2890,11 +2902,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>44.5771598815918</v>
+        <v>44.57716369628906</v>
       </c>
       <c r="C104" t="n">
         <v>74.18000030517578</v>
@@ -2919,7 +2931,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2948,11 +2960,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>48.60784912109375</v>
+        <v>48.60784530639648</v>
       </c>
       <c r="C106" t="n">
         <v>80.52999877929688</v>
@@ -2977,11 +2989,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>47.15316390991211</v>
+        <v>47.15316009521484</v>
       </c>
       <c r="C107" t="n">
         <v>78.12000274658203</v>
@@ -3006,11 +3018,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>50.15304183959961</v>
+        <v>50.15306091308594</v>
       </c>
       <c r="C108" t="n">
         <v>83.08999633789062</v>
@@ -3035,7 +3047,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3064,11 +3076,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>52.79096221923828</v>
+        <v>52.79096603393555</v>
       </c>
       <c r="C110" t="n">
         <v>86.51000213623047</v>
@@ -3093,7 +3105,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3122,11 +3134,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>50.85597229003906</v>
+        <v>50.85596084594727</v>
       </c>
       <c r="C112" t="n">
         <v>82.54000091552734</v>
@@ -3151,7 +3163,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3180,11 +3192,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.24599456787109</v>
+        <v>50.24599838256836</v>
       </c>
       <c r="C114" t="n">
         <v>81.55000305175781</v>
@@ -3209,11 +3221,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>49.96992111206055</v>
+        <v>49.96991729736328</v>
       </c>
       <c r="C115" t="n">
         <v>80.30000305175781</v>
@@ -3238,11 +3250,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>50.97180557250977</v>
+        <v>50.97179794311523</v>
       </c>
       <c r="C116" t="n">
         <v>81.91000366210938</v>
@@ -3267,7 +3279,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3296,7 +3308,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3354,11 +3366,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>54.0262565612793</v>
+        <v>54.02625274658203</v>
       </c>
       <c r="C120" t="n">
         <v>85.91000366210938</v>
@@ -3383,11 +3395,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>54.93244552612305</v>
+        <v>54.93244934082031</v>
       </c>
       <c r="C121" t="n">
         <v>86.44999694824219</v>
@@ -3412,11 +3424,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.77358627319336</v>
+        <v>54.77360153198242</v>
       </c>
       <c r="C122" t="n">
         <v>86.19999694824219</v>
@@ -3441,11 +3453,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>54.96422958374023</v>
+        <v>54.9642219543457</v>
       </c>
       <c r="C123" t="n">
         <v>86.5</v>
@@ -3470,11 +3482,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>55.54047393798828</v>
+        <v>55.54046630859375</v>
       </c>
       <c r="C124" t="n">
         <v>86.5</v>
@@ -3499,11 +3511,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>55.78445816040039</v>
+        <v>55.78446197509766</v>
       </c>
       <c r="C125" t="n">
         <v>86.87999725341797</v>
@@ -3528,7 +3540,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3557,11 +3569,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.74807739257812</v>
+        <v>65.74806213378906</v>
       </c>
       <c r="C127" t="n">
         <v>101.4300003051758</v>
@@ -3586,11 +3598,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>62.89595794677734</v>
+        <v>62.89593505859375</v>
       </c>
       <c r="C128" t="n">
         <v>97.02999877929688</v>
@@ -3615,11 +3627,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>61.43099594116211</v>
+        <v>61.43097305297852</v>
       </c>
       <c r="C129" t="n">
         <v>94.76999664306641</v>
@@ -3644,7 +3656,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3673,7 +3685,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3702,11 +3714,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.62591934204102</v>
+        <v>54.62594223022461</v>
       </c>
       <c r="C132" t="n">
         <v>83.45999908447266</v>
@@ -3731,11 +3743,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>57.41244125366211</v>
+        <v>57.41245269775391</v>
       </c>
       <c r="C133" t="n">
         <v>86.76999664306641</v>
@@ -3760,11 +3772,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>58.11380386352539</v>
+        <v>58.11383056640625</v>
       </c>
       <c r="C134" t="n">
         <v>87.83000183105469</v>
@@ -3789,11 +3801,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>61.88529586791992</v>
+        <v>61.88529205322266</v>
       </c>
       <c r="C135" t="n">
         <v>93.52999877929688</v>
@@ -3818,11 +3830,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>63.16336822509766</v>
+        <v>63.16335296630859</v>
       </c>
       <c r="C136" t="n">
         <v>94.44999694824219</v>
@@ -3847,11 +3859,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>63.2636604309082</v>
+        <v>63.26366806030273</v>
       </c>
       <c r="C137" t="n">
         <v>94.59999847412109</v>
@@ -3876,11 +3888,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>67.97837066650391</v>
+        <v>67.97838592529297</v>
       </c>
       <c r="C138" t="n">
         <v>101.6500015258789</v>
@@ -3905,11 +3917,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>67.62429809570312</v>
+        <v>67.62432861328125</v>
       </c>
       <c r="C139" t="n">
         <v>100.1800003051758</v>
@@ -3934,11 +3946,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>67.89432525634766</v>
+        <v>67.89431762695312</v>
       </c>
       <c r="C140" t="n">
         <v>100.5800018310547</v>
@@ -3963,11 +3975,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>73.20005035400391</v>
+        <v>73.20008087158203</v>
       </c>
       <c r="C141" t="n">
         <v>108.4400024414062</v>
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>72.94229125976562</v>
+        <v>72.94227600097656</v>
       </c>
       <c r="C143" t="n">
         <v>107.0800018310547</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>76.97493743896484</v>
+        <v>76.97495269775391</v>
       </c>
       <c r="C144" t="n">
         <v>113</v>
@@ -4079,7 +4091,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4108,11 +4120,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>77.54940795898438</v>
+        <v>77.54942321777344</v>
       </c>
       <c r="C146" t="n">
         <v>112.7699966430664</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>75.68580627441406</v>
+        <v>75.68581390380859</v>
       </c>
       <c r="C147" t="n">
         <v>110.0599975585938</v>
@@ -4166,11 +4178,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>76.08917236328125</v>
+        <v>76.08918762207031</v>
       </c>
       <c r="C148" t="n">
         <v>109.6100006103516</v>
@@ -4195,7 +4207,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4224,7 +4236,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4253,11 +4265,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>75.63233184814453</v>
+        <v>75.63232421875</v>
       </c>
       <c r="C151" t="n">
         <v>107.8199996948242</v>
@@ -4282,11 +4294,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>77.74375152587891</v>
+        <v>77.74374389648438</v>
       </c>
       <c r="C152" t="n">
         <v>110.8300018310547</v>
@@ -4311,11 +4323,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>79.98843383789062</v>
+        <v>79.98844146728516</v>
       </c>
       <c r="C153" t="n">
         <v>114.0299987792969</v>
@@ -4340,11 +4352,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>78.83210754394531</v>
+        <v>78.83207702636719</v>
       </c>
       <c r="C154" t="n">
         <v>111.3300018310547</v>
@@ -4369,11 +4381,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>76.99812316894531</v>
+        <v>76.99813079833984</v>
       </c>
       <c r="C155" t="n">
         <v>108.7399978637695</v>
@@ -4398,11 +4410,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>81.35997009277344</v>
+        <v>81.35999298095703</v>
       </c>
       <c r="C156" t="n">
         <v>114.9000015258789</v>
@@ -4427,11 +4439,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>77.67695617675781</v>
+        <v>77.67694091796875</v>
       </c>
       <c r="C157" t="n">
         <v>108.629997253418</v>
@@ -4456,11 +4468,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>83.70489501953125</v>
+        <v>83.70488739013672</v>
       </c>
       <c r="C158" t="n">
         <v>117.0599975585938</v>
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>84.91336822509766</v>
+        <v>84.91337585449219</v>
       </c>
       <c r="C159" t="n">
         <v>118.75</v>
@@ -4514,11 +4526,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>92.35883331298828</v>
+        <v>92.35882568359375</v>
       </c>
       <c r="C160" t="n">
         <v>128</v>
@@ -4543,11 +4555,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>90.75698089599609</v>
+        <v>90.75698852539062</v>
       </c>
       <c r="C161" t="n">
         <v>125.7799987792969</v>
@@ -4572,11 +4584,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>93.80915069580078</v>
+        <v>93.80916595458984</v>
       </c>
       <c r="C162" t="n">
         <v>130.0099945068359</v>
@@ -4601,11 +4613,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>94.84433746337891</v>
+        <v>94.84432983398438</v>
       </c>
       <c r="C163" t="n">
         <v>130.3500061035156</v>
@@ -4630,11 +4642,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>96.96167755126953</v>
+        <v>96.96166229248047</v>
       </c>
       <c r="C164" t="n">
         <v>133.2599945068359</v>
@@ -4659,11 +4671,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>105.6275482177734</v>
+        <v>105.627555847168</v>
       </c>
       <c r="C165" t="n">
         <v>145.1699981689453</v>
@@ -4688,11 +4700,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>101.972785949707</v>
+        <v>101.9728088378906</v>
       </c>
       <c r="C166" t="n">
         <v>139.0099945068359</v>
@@ -4717,11 +4729,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>101.8114166259766</v>
+        <v>101.8114013671875</v>
       </c>
       <c r="C167" t="n">
         <v>138.7899932861328</v>
@@ -4746,11 +4758,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>98.04823303222656</v>
+        <v>98.04822540283203</v>
       </c>
       <c r="C168" t="n">
         <v>133.6600036621094</v>
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4804,11 +4816,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>110.906005859375</v>
+        <v>110.9059677124023</v>
       </c>
       <c r="C170" t="n">
         <v>149.8399963378906</v>
@@ -4833,11 +4845,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>106.0579223632812</v>
+        <v>106.0579376220703</v>
       </c>
       <c r="C171" t="n">
         <v>143.2899932861328</v>
@@ -4862,11 +4874,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>107.7197036743164</v>
+        <v>107.7196731567383</v>
       </c>
       <c r="C172" t="n">
         <v>144.3999938964844</v>
@@ -4891,11 +4903,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>118.9318008422852</v>
+        <v>118.9318237304688</v>
       </c>
       <c r="C173" t="n">
         <v>159.4299926757812</v>
@@ -4920,11 +4932,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>128.4281311035156</v>
+        <v>128.4281158447266</v>
       </c>
       <c r="C174" t="n">
         <v>172.1600036621094</v>
@@ -4949,11 +4961,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>125.7064819335938</v>
+        <v>125.7064895629883</v>
       </c>
       <c r="C175" t="n">
         <v>167.3500061035156</v>
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>127.8547897338867</v>
+        <v>127.8547592163086</v>
       </c>
       <c r="C176" t="n">
         <v>170.2100067138672</v>
@@ -5007,11 +5019,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>122.6267242431641</v>
+        <v>122.6267166137695</v>
       </c>
       <c r="C177" t="n">
         <v>163.25</v>
@@ -5036,11 +5048,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>126.0215606689453</v>
+        <v>126.0215148925781</v>
       </c>
       <c r="C178" t="n">
         <v>166.5</v>
@@ -5065,7 +5077,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5094,11 +5106,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>126.8314208984375</v>
+        <v>126.8314056396484</v>
       </c>
       <c r="C180" t="n">
         <v>167.5700073242188</v>
@@ -5123,11 +5135,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>121.5136413574219</v>
+        <v>121.5136260986328</v>
       </c>
       <c r="C181" t="n">
         <v>159.1900024414062</v>
@@ -5152,11 +5164,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.5671081542969</v>
+        <v>121.5670852661133</v>
       </c>
       <c r="C182" t="n">
         <v>159.2599945068359</v>
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>118.8878173828125</v>
+        <v>118.8878021240234</v>
       </c>
       <c r="C183" t="n">
         <v>155.75</v>
@@ -5210,11 +5222,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.5228271484375</v>
+        <v>132.5227661132812</v>
       </c>
       <c r="C184" t="n">
         <v>172.1300048828125</v>
@@ -5239,11 +5251,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>145.5571746826172</v>
+        <v>145.5571899414062</v>
       </c>
       <c r="C185" t="n">
         <v>189.0599975585938</v>
@@ -5268,7 +5280,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5297,11 +5309,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>151.2117309570312</v>
+        <v>151.2117156982422</v>
       </c>
       <c r="C187" t="n">
         <v>195.1000061035156</v>
@@ -5326,11 +5338,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>149.6539001464844</v>
+        <v>149.6538543701172</v>
       </c>
       <c r="C188" t="n">
         <v>193.0899963378906</v>
@@ -5355,11 +5367,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>150.8939819335938</v>
+        <v>150.8939666748047</v>
       </c>
       <c r="C189" t="n">
         <v>194.6900024414062</v>
@@ -5384,11 +5396,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>135.279052734375</v>
+        <v>135.2790374755859</v>
       </c>
       <c r="C190" t="n">
         <v>173.3200073242188</v>
@@ -5413,11 +5425,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>140.7270050048828</v>
+        <v>140.7269897460938</v>
       </c>
       <c r="C191" t="n">
         <v>180.3000030517578</v>
@@ -5442,7 +5454,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5471,11 +5483,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>164.1396179199219</v>
+        <v>164.1396636962891</v>
       </c>
       <c r="C193" t="n">
         <v>208.7400054931641</v>
@@ -5500,11 +5512,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>143.5140533447266</v>
+        <v>143.5140686035156</v>
       </c>
       <c r="C194" t="n">
         <v>182.5099945068359</v>
@@ -5529,11 +5541,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>130.9955902099609</v>
+        <v>130.9955596923828</v>
       </c>
       <c r="C195" t="n">
         <v>166.5899963378906</v>
@@ -5558,11 +5570,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>146.3969116210938</v>
+        <v>146.3969573974609</v>
       </c>
       <c r="C196" t="n">
         <v>184.6000061035156</v>
@@ -5587,11 +5599,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>146.8806915283203</v>
+        <v>146.8807067871094</v>
       </c>
       <c r="C197" t="n">
         <v>185.2100067138672</v>
@@ -5616,11 +5628,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>150.4018249511719</v>
+        <v>150.4018096923828</v>
       </c>
       <c r="C198" t="n">
         <v>189.6499938964844</v>
@@ -5645,11 +5657,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>134.7264556884766</v>
+        <v>134.7264404296875</v>
       </c>
       <c r="C199" t="n">
         <v>168.3800048828125</v>
@@ -5674,7 +5686,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5703,11 +5715,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>136.6868133544922</v>
+        <v>136.6867828369141</v>
       </c>
       <c r="C201" t="n">
         <v>170.8300018310547</v>
@@ -5732,11 +5744,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>116.6733474731445</v>
+        <v>116.6733627319336</v>
       </c>
       <c r="C202" t="n">
         <v>144.5500030517578</v>
@@ -5761,7 +5773,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5790,11 +5802,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>114.1550445556641</v>
+        <v>114.1550140380859</v>
       </c>
       <c r="C204" t="n">
         <v>141.4299926757812</v>
@@ -5819,7 +5831,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5848,11 +5860,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>120.851432800293</v>
+        <v>120.8514175415039</v>
       </c>
       <c r="C206" t="n">
         <v>148.1100006103516</v>
@@ -5877,7 +5889,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5906,7 +5918,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5935,11 +5947,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>101.6545028686523</v>
+        <v>101.6545104980469</v>
       </c>
       <c r="C209" t="n">
         <v>123.0899963378906</v>
@@ -5964,7 +5976,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5993,11 +6005,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>95.38933563232422</v>
+        <v>95.38930511474609</v>
       </c>
       <c r="C211" t="n">
         <v>113.9400024414062</v>
@@ -6022,7 +6034,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6051,11 +6063,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>84.13750457763672</v>
+        <v>84.13749694824219</v>
       </c>
       <c r="C213" t="n">
         <v>100.5</v>
@@ -6080,7 +6092,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6109,7 +6121,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6138,11 +6150,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>99.78825378417969</v>
+        <v>99.78824615478516</v>
       </c>
       <c r="C216" t="n">
         <v>117.2799987792969</v>
@@ -6167,11 +6179,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>99.34147644042969</v>
+        <v>99.34150695800781</v>
       </c>
       <c r="C217" t="n">
         <v>115.1900024414062</v>
@@ -6196,11 +6208,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>93.3563232421875</v>
+        <v>93.35633087158203</v>
       </c>
       <c r="C218" t="n">
         <v>108.25</v>
@@ -6225,11 +6237,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>94.81381988525391</v>
+        <v>94.81380462646484</v>
       </c>
       <c r="C219" t="n">
         <v>109.9400024414062</v>
@@ -6254,11 +6266,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>92.58545684814453</v>
+        <v>92.58546447753906</v>
       </c>
       <c r="C220" t="n">
         <v>105.8300018310547</v>
@@ -6283,11 +6295,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>82.04349517822266</v>
+        <v>82.04351043701172</v>
       </c>
       <c r="C221" t="n">
         <v>93.77999877929688</v>
@@ -6312,11 +6324,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>89.67220306396484</v>
+        <v>89.67219543457031</v>
       </c>
       <c r="C222" t="n">
         <v>102.5</v>
@@ -6341,11 +6353,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>86.83418273925781</v>
+        <v>86.83419036865234</v>
       </c>
       <c r="C223" t="n">
         <v>97.69999694824219</v>
@@ -6370,7 +6382,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6399,11 +6411,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56156158447266</v>
+        <v>99.56157684326172</v>
       </c>
       <c r="C225" t="n">
         <v>112.0199966430664</v>
@@ -6428,7 +6440,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6457,7 +6469,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6486,7 +6498,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6515,7 +6527,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6544,11 +6556,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>81.70203399658203</v>
+        <v>81.7020263671875</v>
       </c>
       <c r="C230" t="n">
         <v>89.27999877929688</v>
@@ -6573,11 +6585,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>86.1129150390625</v>
+        <v>86.11290740966797</v>
       </c>
       <c r="C231" t="n">
         <v>94.09999847412109</v>
@@ -6602,11 +6614,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>96.97917938232422</v>
+        <v>96.97917175292969</v>
       </c>
       <c r="C232" t="n">
         <v>104.2300033569336</v>
@@ -6629,11 +6641,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>98.40274810791016</v>
+        <v>98.40274047851562</v>
       </c>
       <c r="C233" t="n">
         <v>105.7600021362305</v>
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>93.36910247802734</v>
+        <v>93.36909484863281</v>
       </c>
       <c r="C234" t="n">
         <v>100.3499984741211</v>
@@ -6683,11 +6695,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>96.61019134521484</v>
+        <v>96.61018371582031</v>
       </c>
       <c r="C235" t="n">
         <v>102.7300033569336</v>
@@ -6710,7 +6722,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6737,11 +6749,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>93.23403930664062</v>
+        <v>93.23404693603516</v>
       </c>
       <c r="C237" t="n">
         <v>99.13999938964844</v>
@@ -6764,7 +6776,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6791,7 +6803,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6845,11 +6857,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>85.51709747314453</v>
+        <v>85.51708984375</v>
       </c>
       <c r="C241" t="n">
         <v>88.87000274658203</v>
@@ -6872,7 +6884,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6957,11 +6969,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>86.49827575683594</v>
+        <v>86.49826812744141</v>
       </c>
       <c r="C245" t="n">
         <v>88.77999877929688</v>
@@ -6986,11 +6998,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>89.14836120605469</v>
+        <v>89.14836883544922</v>
       </c>
       <c r="C246" t="n">
         <v>91.5</v>
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7102,32 +7114,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>70.23000335693359</v>
+        <v>67.62999725341797</v>
       </c>
       <c r="C250" t="n">
-        <v>70.23000335693359</v>
+        <v>67.62999725341797</v>
       </c>
       <c r="D250" t="n">
-        <v>55902700</v>
+        <v>60498500</v>
       </c>
       <c r="E250" t="n">
         <v>1.97</v>
       </c>
       <c r="F250" t="n">
-        <v>35.6497478969206</v>
+        <v>34.3299478443746</v>
       </c>
       <c r="G250" t="n">
         <v>425455439</v>
       </c>
       <c r="H250" t="n">
-        <v>29879736909.19566</v>
+        <v>28773550171.02174</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1313949590852451</v>
+        <v>0.1421970304156812</v>
       </c>
     </row>
   </sheetData>
@@ -7159,75 +7171,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7263,13 +7275,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7422,7 +7434,7 @@
       <c r="I6" t="n">
         <v>-0.47</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K6" t="n">
@@ -7435,13 +7447,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7468,7 +7480,7 @@
       <c r="I7" t="n">
         <v>-0.9199999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K7" t="n">
@@ -7481,13 +7493,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7514,7 +7526,7 @@
       <c r="I8" t="n">
         <v>-0.8509151286353468</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K8" t="n">
@@ -7527,13 +7539,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7560,7 +7572,7 @@
       <c r="I9" t="n">
         <v>-1.210915128635347</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K9" t="n">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7606,7 +7618,7 @@
       <c r="I10" t="n">
         <v>-1.140915128635347</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K10" t="n">
@@ -7619,13 +7631,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7652,7 +7664,7 @@
       <c r="I11" t="n">
         <v>-0.5909151286353469</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K11" t="n">
@@ -7665,13 +7677,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7698,7 +7710,7 @@
       <c r="I12" t="n">
         <v>-0.1600000000000002</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K12" t="n">
@@ -7711,13 +7723,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7744,7 +7756,7 @@
       <c r="I13" t="n">
         <v>0.4799999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K13" t="n">
@@ -7757,13 +7769,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7790,7 +7802,7 @@
       <c r="I14" t="n">
         <v>0.52</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K14" t="n">
@@ -7803,13 +7815,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7836,7 +7848,7 @@
       <c r="I15" t="n">
         <v>0.57</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K15" t="n">
@@ -7849,13 +7861,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7882,7 +7894,7 @@
       <c r="I16" t="n">
         <v>0.88</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K16" t="n">
@@ -7895,13 +7907,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7928,7 +7940,7 @@
       <c r="I17" t="n">
         <v>0.87</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K17" t="n">
@@ -7941,13 +7953,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7974,7 +7986,7 @@
       <c r="I18" t="n">
         <v>0.6399999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="K18" t="n">
@@ -7987,13 +7999,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8020,7 +8032,7 @@
       <c r="I19" t="n">
         <v>0.52</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K19" t="n">
@@ -8033,13 +8045,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8066,7 +8078,7 @@
       <c r="I20" t="n">
         <v>0.2999999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K20" t="n">
@@ -8079,13 +8091,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8112,7 +8124,7 @@
       <c r="I21" t="n">
         <v>0.32</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K21" t="n">
@@ -8125,13 +8137,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8158,7 +8170,7 @@
       <c r="I22" t="n">
         <v>0.2799999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="K22" t="n">
@@ -8171,13 +8183,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8204,7 +8216,7 @@
       <c r="I23" t="n">
         <v>0.4999999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K23" t="n">
@@ -8217,13 +8229,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8250,7 +8262,7 @@
       <c r="I24" t="n">
         <v>0.39</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K24" t="n">
@@ -8263,13 +8275,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8296,7 +8308,7 @@
       <c r="I25" t="n">
         <v>0.5199999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K25" t="n">
@@ -8309,13 +8321,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8342,7 +8354,7 @@
       <c r="I26" t="n">
         <v>1.04</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K26" t="n">
@@ -8355,13 +8367,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8388,7 +8400,7 @@
       <c r="I27" t="n">
         <v>1.11</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K27" t="n">
@@ -8401,13 +8413,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8434,7 +8446,7 @@
       <c r="I28" t="n">
         <v>4.46</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K28" t="n">
@@ -8447,13 +8459,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8480,7 +8492,7 @@
       <c r="I29" t="n">
         <v>4.45</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K29" t="n">
@@ -8493,13 +8505,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8526,7 +8538,7 @@
       <c r="I30" t="n">
         <v>4.43</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="K30" t="n">
@@ -8539,13 +8551,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8572,7 +8584,7 @@
       <c r="I31" t="n">
         <v>4.2</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="K31" t="n">
@@ -8585,13 +8597,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8618,7 +8630,7 @@
       <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K32" t="n">
@@ -8631,13 +8643,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8664,7 +8676,7 @@
       <c r="I33" t="n">
         <v>0.98</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K33" t="n">
@@ -8677,13 +8689,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8710,7 +8722,7 @@
       <c r="I34" t="n">
         <v>0.95</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K34" t="n">
@@ -8723,13 +8735,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8756,7 +8768,7 @@
       <c r="I35" t="n">
         <v>1.17</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K35" t="n">
@@ -8769,13 +8781,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8802,7 +8814,7 @@
       <c r="I36" t="n">
         <v>1.26</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="K36" t="n">
@@ -8815,13 +8827,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8848,7 +8860,7 @@
       <c r="I37" t="n">
         <v>1.21</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K37" t="n">
@@ -8861,13 +8873,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8894,7 +8906,7 @@
       <c r="I38" t="n">
         <v>1.02</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="K38" t="n">
@@ -8907,13 +8919,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8940,7 +8952,7 @@
       <c r="I39" t="n">
         <v>0.9</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K39" t="n">
@@ -8953,13 +8965,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8986,7 +8998,7 @@
       <c r="I40" t="n">
         <v>0.9500000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K40" t="n">
@@ -8999,13 +9011,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9032,7 +9044,7 @@
       <c r="I41" t="n">
         <v>1.07</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K41" t="n">
@@ -9045,13 +9057,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9078,7 +9090,7 @@
       <c r="I42" t="n">
         <v>1.34</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="K42" t="n">
@@ -9091,13 +9103,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9124,7 +9136,7 @@
       <c r="I43" t="n">
         <v>1.57</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K43" t="n">
@@ -9137,13 +9149,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9170,7 +9182,7 @@
       <c r="I44" t="n">
         <v>1.73</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K44" t="n">
@@ -9183,13 +9195,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9216,7 +9228,7 @@
       <c r="I45" t="n">
         <v>1.98</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K45" t="n">
@@ -9229,13 +9241,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43900</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9262,7 +9274,7 @@
       <c r="I46" t="n">
         <v>1.97</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43900</v>
       </c>
       <c r="K46" t="n">
@@ -9275,13 +9287,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9308,7 +9320,7 @@
       <c r="I47" t="n">
         <v>1.91</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K47" t="n">
@@ -9321,13 +9333,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9354,7 +9366,7 @@
       <c r="I48" t="n">
         <v>1.8</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K48" t="n">
@@ -9367,13 +9379,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9400,7 +9412,7 @@
       <c r="I49" t="n">
         <v>1.6</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K49" t="n">
@@ -9413,13 +9425,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9446,7 +9458,7 @@
       <c r="I50" t="n">
         <v>2.35</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="K50" t="n">
@@ -9459,13 +9471,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9492,7 +9504,7 @@
       <c r="I51" t="n">
         <v>2.1</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="K51" t="n">
@@ -9505,13 +9517,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9538,7 +9550,7 @@
       <c r="I52" t="n">
         <v>2.46</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K52" t="n">
@@ -9551,13 +9563,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9584,7 +9596,7 @@
       <c r="I53" t="n">
         <v>2.89</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K53" t="n">
@@ -9597,13 +9609,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9630,7 +9642,7 @@
       <c r="I54" t="n">
         <v>2.53</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9643,13 +9655,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9676,7 +9688,7 @@
       <c r="I55" t="n">
         <v>3.37</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K55" t="n">
@@ -9689,13 +9701,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9722,7 +9734,7 @@
       <c r="I56" t="n">
         <v>3.57</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K56" t="n">
@@ -9735,13 +9747,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9768,7 +9780,7 @@
       <c r="I57" t="n">
         <v>3.73</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K57" t="n">
@@ -9781,13 +9793,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9814,7 +9826,7 @@
       <c r="I58" t="n">
         <v>3.86</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K58" t="n">
@@ -9827,13 +9839,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9860,7 +9872,7 @@
       <c r="I59" t="n">
         <v>3.859999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K59" t="n">
@@ -9873,13 +9885,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9906,7 +9918,7 @@
       <c r="I60" t="n">
         <v>3.94</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K60" t="n">
@@ -9919,13 +9931,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9952,7 +9964,7 @@
       <c r="I61" t="n">
         <v>3.58</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K61" t="n">
@@ -9965,13 +9977,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9998,7 +10010,7 @@
       <c r="I62" t="n">
         <v>3.46</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K62" t="n">
@@ -10011,13 +10023,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10044,7 +10056,7 @@
       <c r="I63" t="n">
         <v>3.2</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K63" t="n">
@@ -10057,13 +10069,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10090,7 +10102,7 @@
       <c r="I64" t="n">
         <v>2.73</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K64" t="n">
@@ -10103,13 +10115,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10136,7 +10148,7 @@
       <c r="I65" t="n">
         <v>2.82</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K65" t="n">
@@ -10149,13 +10161,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10182,7 +10194,7 @@
       <c r="I66" t="n">
         <v>-8.98</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="K66" t="n">
@@ -10195,13 +10207,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10228,7 +10240,7 @@
       <c r="I67" t="n">
         <v>-10.76</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="K67" t="n">
@@ -10241,13 +10253,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10274,7 +10286,7 @@
       <c r="I68" t="n">
         <v>-10.67</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K68" t="n">
@@ -10287,13 +10299,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10320,7 +10332,7 @@
       <c r="I69" t="n">
         <v>-10.63</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K69" t="n">
@@ -10333,13 +10345,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10366,7 +10378,7 @@
       <c r="I70" t="n">
         <v>1.01</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="K70" t="n">
@@ -10379,13 +10391,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10412,7 +10424,7 @@
       <c r="I71" t="n">
         <v>2.42</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K71" t="n">
@@ -10425,13 +10437,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10458,7 +10470,7 @@
       <c r="I72" t="n">
         <v>1.97</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K72" t="n">
@@ -10495,52 +10507,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="C2" t="n">
@@ -10569,10 +10581,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10601,10 +10613,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40214</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40225</v>
       </c>
       <c r="C4" t="n">
@@ -10633,10 +10645,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="C5" t="n">
@@ -10665,10 +10677,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="C6" t="n">
@@ -10697,10 +10709,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10729,10 +10741,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40579</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C8" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40945</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="C12" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41310</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41317</v>
       </c>
       <c r="C16" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41393</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C17" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41485</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C19" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C20" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41761</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C21" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41855</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C22" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41946</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C23" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C24" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42128</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C25" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42221</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C26" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42312</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C27" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42415</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="C28" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42495</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="C29" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C30" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C31" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42781</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C32" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42857</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42951</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="C34" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43041</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C35" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43152</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="C36" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C37" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43315</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C38" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C39" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43518</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="C40" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C41" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C43" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43896</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43900</v>
       </c>
       <c r="C44" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="C48" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44315</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="C49" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44411</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C50" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44502</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C51" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C52" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44677</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44775</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C54" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44867</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C55" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44978</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C56" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45342</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C60" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C62" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C63" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45728</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="C64" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45784</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="C65" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45965</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C67" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46072</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="C68" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46147</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C69" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46237</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12763,12 +12775,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CCI.xlsx
+++ b/salidas/empresas/CCI.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>18.82826232910156</v>
+        <v>18.82826614379883</v>
       </c>
       <c r="C2" t="n">
         <v>31.6299991607666</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.66159057617188</v>
+        <v>18.66158866882324</v>
       </c>
       <c r="C3" t="n">
         <v>31.35000038146973</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.87578582763672</v>
+        <v>16.87579345703125</v>
       </c>
       <c r="C4" t="n">
         <v>28.35000038146973</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>20.03070259094238</v>
+        <v>20.03070449829102</v>
       </c>
       <c r="C5" t="n">
         <v>33.65000152587891</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.9116039276123</v>
+        <v>18.91159629821777</v>
       </c>
       <c r="C6" t="n">
         <v>31.77000045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>20.56048965454102</v>
+        <v>20.56048774719238</v>
       </c>
       <c r="C7" t="n">
         <v>34.54000091552734</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>20.97122192382812</v>
+        <v>20.97122573852539</v>
       </c>
       <c r="C8" t="n">
         <v>35.22999954223633</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.45333480834961</v>
+        <v>20.45333862304688</v>
       </c>
       <c r="C9" t="n">
         <v>34.36000061035156</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.97718048095703</v>
+        <v>20.9771728515625</v>
       </c>
       <c r="C10" t="n">
         <v>35.2400016784668</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.03070259094238</v>
+        <v>20.03070449829102</v>
       </c>
       <c r="C11" t="n">
         <v>33.65000152587891</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.51287078857422</v>
+        <v>20.51286506652832</v>
       </c>
       <c r="C12" t="n">
         <v>34.45999908447266</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.9295539855957</v>
+        <v>20.9295482635498</v>
       </c>
       <c r="C14" t="n">
         <v>35.15999984741211</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.47114944458008</v>
+        <v>19.47115516662598</v>
       </c>
       <c r="C15" t="n">
         <v>32.70999908447266</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.12590217590332</v>
+        <v>19.12589836120605</v>
       </c>
       <c r="C16" t="n">
         <v>32.13000106811523</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>20.44144058227539</v>
+        <v>20.44144248962402</v>
       </c>
       <c r="C17" t="n">
         <v>34.34000015258789</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.59029579162598</v>
+        <v>21.59030342102051</v>
       </c>
       <c r="C19" t="n">
         <v>36.27000045776367</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>21.57839775085449</v>
+        <v>21.57840347290039</v>
       </c>
       <c r="C20" t="n">
         <v>36.25</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>21.88197898864746</v>
+        <v>21.88197708129883</v>
       </c>
       <c r="C21" t="n">
         <v>36.7599983215332</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>24.1856575012207</v>
+        <v>24.18566513061523</v>
       </c>
       <c r="C22" t="n">
         <v>40.63000106811523</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>24.44757080078125</v>
+        <v>24.44757843017578</v>
       </c>
       <c r="C23" t="n">
         <v>41.06999969482422</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>24.97140502929688</v>
+        <v>24.97141075134277</v>
       </c>
       <c r="C24" t="n">
         <v>41.95000076293945</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>24.7630615234375</v>
+        <v>24.7630729675293</v>
       </c>
       <c r="C25" t="n">
         <v>41.59999847412109</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>21.50101661682129</v>
+        <v>21.50100517272949</v>
       </c>
       <c r="C26" t="n">
         <v>36.11999893188477</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.48315620422363</v>
+        <v>21.48314666748047</v>
       </c>
       <c r="C27" t="n">
         <v>36.09000015258789</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.12608337402344</v>
+        <v>23.1260871887207</v>
       </c>
       <c r="C29" t="n">
         <v>38.84999847412109</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>25.29284477233887</v>
+        <v>25.29285430908203</v>
       </c>
       <c r="C30" t="n">
         <v>42.4900016784668</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>23.05465888977051</v>
+        <v>23.05465698242188</v>
       </c>
       <c r="C31" t="n">
         <v>38.72999954223633</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>22.73916816711426</v>
+        <v>22.73916435241699</v>
       </c>
       <c r="C32" t="n">
         <v>38.20000076293945</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.26295471191406</v>
+        <v>22.2629508972168</v>
       </c>
       <c r="C33" t="n">
         <v>37.40000152587891</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>17.2448558807373</v>
+        <v>17.24485397338867</v>
       </c>
       <c r="C34" t="n">
         <v>28.96999931335449</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.60177898406982</v>
+        <v>12.60178089141846</v>
       </c>
       <c r="C35" t="n">
         <v>21.17000007629395</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>8.375394821166992</v>
+        <v>8.375393867492676</v>
       </c>
       <c r="C36" t="n">
         <v>14.06999969482422</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.46477699279785</v>
+        <v>10.4647741317749</v>
       </c>
       <c r="C37" t="n">
         <v>17.57999992370605</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.61959457397461</v>
+        <v>11.61959362030029</v>
       </c>
       <c r="C38" t="n">
         <v>19.52000045776367</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.44096755981445</v>
+        <v>10.44096851348877</v>
       </c>
       <c r="C39" t="n">
         <v>17.54000091552734</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.14937877655029</v>
+        <v>12.14938068389893</v>
       </c>
       <c r="C40" t="n">
         <v>20.40999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.59591960906982</v>
+        <v>14.59592533111572</v>
       </c>
       <c r="C41" t="n">
         <v>24.52000045776367</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.44115352630615</v>
+        <v>14.44115257263184</v>
       </c>
       <c r="C42" t="n">
         <v>24.26000022888184</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.29829025268555</v>
+        <v>14.29828643798828</v>
       </c>
       <c r="C43" t="n">
         <v>24.02000045776367</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.10794639587402</v>
+        <v>17.10794830322266</v>
       </c>
       <c r="C44" t="n">
         <v>28.73999977111816</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.66754150390625</v>
+        <v>18.66754341125488</v>
       </c>
       <c r="C46" t="n">
         <v>31.36000061035156</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>17.98894309997559</v>
+        <v>17.98893737792969</v>
       </c>
       <c r="C47" t="n">
         <v>30.21999931335449</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.84030914306641</v>
+        <v>21.84031105041504</v>
       </c>
       <c r="C48" t="n">
         <v>36.68999862670898</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.23918914794922</v>
+        <v>23.23918724060059</v>
       </c>
       <c r="C49" t="n">
         <v>39.04000091552734</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.98911666870117</v>
+        <v>21.98912620544434</v>
       </c>
       <c r="C50" t="n">
         <v>36.93999862670898</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.50105094909668</v>
+        <v>22.50104904174805</v>
       </c>
       <c r="C51" t="n">
         <v>37.79999923706055</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.75702857971191</v>
+        <v>22.75702095031738</v>
       </c>
       <c r="C52" t="n">
         <v>38.22999954223633</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.53081893920898</v>
+        <v>22.53081321716309</v>
       </c>
       <c r="C53" t="n">
         <v>37.84999847412109</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.51896095275879</v>
+        <v>23.51896476745605</v>
       </c>
       <c r="C56" t="n">
         <v>39.5099983215332</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>24.47734451293945</v>
+        <v>24.47734069824219</v>
       </c>
       <c r="C57" t="n">
         <v>41.11999893188477</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>25.66786766052246</v>
+        <v>25.66787338256836</v>
       </c>
       <c r="C59" t="n">
         <v>43.11999893188477</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.72735023498535</v>
+        <v>24.72735595703125</v>
       </c>
       <c r="C60" t="n">
         <v>41.54000091552734</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>26.09050369262695</v>
+        <v>26.09050941467285</v>
       </c>
       <c r="C61" t="n">
         <v>43.83000183105469</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.10237121582031</v>
+        <v>25.10235786437988</v>
       </c>
       <c r="C62" t="n">
         <v>42.16999816894531</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>25.09046363830566</v>
+        <v>25.09045600891113</v>
       </c>
       <c r="C63" t="n">
         <v>42.15000152587891</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>25.32857322692871</v>
+        <v>25.32856559753418</v>
       </c>
       <c r="C64" t="n">
         <v>42.54999923706055</v>
@@ -1815,7 +1815,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.51309776306152</v>
+        <v>25.51309967041016</v>
       </c>
       <c r="C65" t="n">
         <v>42.86000061035156</v>
@@ -1840,7 +1840,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.64996528625488</v>
+        <v>24.64996910095215</v>
       </c>
       <c r="C66" t="n">
         <v>41.40999984741211</v>
@@ -1865,7 +1865,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.28089714050293</v>
+        <v>24.28090858459473</v>
       </c>
       <c r="C67" t="n">
         <v>40.79000091552734</v>
@@ -1890,7 +1890,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>25.83454132080078</v>
+        <v>25.83454895019531</v>
       </c>
       <c r="C68" t="n">
         <v>43.40000152587891</v>
@@ -1915,7 +1915,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>25.85240364074707</v>
+        <v>25.85239410400391</v>
       </c>
       <c r="C69" t="n">
         <v>43.43000030517578</v>
@@ -1940,7 +1940,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>24.2094669342041</v>
+        <v>24.20947265625</v>
       </c>
       <c r="C70" t="n">
         <v>40.66999816894531</v>
@@ -1965,7 +1965,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>24.62019157409668</v>
+        <v>24.62019920349121</v>
       </c>
       <c r="C71" t="n">
         <v>41.36000061035156</v>
@@ -1990,7 +1990,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>25.19165992736816</v>
+        <v>25.19166564941406</v>
       </c>
       <c r="C72" t="n">
         <v>42.31999969482422</v>
@@ -2015,7 +2015,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.66792106628418</v>
+        <v>26.66792297363281</v>
       </c>
       <c r="C73" t="n">
         <v>44.79999923706055</v>
@@ -2065,7 +2065,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>30.84072685241699</v>
+        <v>30.84073257446289</v>
       </c>
       <c r="C75" t="n">
         <v>51.81000137329102</v>
@@ -2094,7 +2094,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>31.75149917602539</v>
+        <v>31.75150108337402</v>
       </c>
       <c r="C76" t="n">
         <v>53.34000015258789</v>
@@ -2123,7 +2123,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.69802474975586</v>
+        <v>33.69800567626953</v>
       </c>
       <c r="C77" t="n">
         <v>56.61000061035156</v>
@@ -2181,7 +2181,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.91831207275391</v>
+        <v>34.91830062866211</v>
       </c>
       <c r="C79" t="n">
         <v>58.65999984741211</v>
@@ -2210,7 +2210,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>36.83506393432617</v>
+        <v>36.83505630493164</v>
       </c>
       <c r="C80" t="n">
         <v>61.88000106811523</v>
@@ -2239,7 +2239,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>37.77557754516602</v>
+        <v>37.77559280395508</v>
       </c>
       <c r="C81" t="n">
         <v>63.45999908447266</v>
@@ -2268,7 +2268,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>38.15656280517578</v>
+        <v>38.15655136108398</v>
       </c>
       <c r="C82" t="n">
         <v>64.09999847412109</v>
@@ -2297,7 +2297,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>39.73401260375977</v>
+        <v>39.73401641845703</v>
       </c>
       <c r="C83" t="n">
         <v>66.75</v>
@@ -2326,7 +2326,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>40.19235992431641</v>
+        <v>40.19237899780273</v>
       </c>
       <c r="C84" t="n">
         <v>67.51999664306641</v>
@@ -2355,7 +2355,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>42.95440292358398</v>
+        <v>42.95440673828125</v>
       </c>
       <c r="C85" t="n">
         <v>72.16000366210938</v>
@@ -2384,7 +2384,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.97814559936523</v>
+        <v>41.9781494140625</v>
       </c>
       <c r="C86" t="n">
         <v>70.51999664306641</v>
@@ -2413,7 +2413,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.5495719909668</v>
+        <v>41.54956817626953</v>
       </c>
       <c r="C87" t="n">
         <v>69.80000305175781</v>
@@ -2442,7 +2442,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>41.45433044433594</v>
+        <v>41.45432662963867</v>
       </c>
       <c r="C88" t="n">
         <v>69.63999938964844</v>
@@ -2471,7 +2471,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>45.83548736572266</v>
+        <v>45.83549499511719</v>
       </c>
       <c r="C89" t="n">
         <v>77</v>
@@ -2500,7 +2500,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>42.4127197265625</v>
+        <v>42.41270065307617</v>
       </c>
       <c r="C90" t="n">
         <v>71.25</v>
@@ -2558,7 +2558,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>41.81743240356445</v>
+        <v>41.81744003295898</v>
       </c>
       <c r="C92" t="n">
         <v>70.25</v>
@@ -2587,7 +2587,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>41.3233757019043</v>
+        <v>41.32335662841797</v>
       </c>
       <c r="C93" t="n">
         <v>69.41999816894531</v>
@@ -2645,7 +2645,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>45.25211334228516</v>
+        <v>45.25211715698242</v>
       </c>
       <c r="C95" t="n">
         <v>76.01999664306641</v>
@@ -2674,7 +2674,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>44.18659210205078</v>
+        <v>44.18659591674805</v>
       </c>
       <c r="C96" t="n">
         <v>74.23000335693359</v>
@@ -2703,7 +2703,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>43.71039581298828</v>
+        <v>43.71038436889648</v>
       </c>
       <c r="C97" t="n">
         <v>73.43000030517578</v>
@@ -2732,7 +2732,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.24006271362305</v>
+        <v>42.24008178710938</v>
       </c>
       <c r="C98" t="n">
         <v>70.95999908447266</v>
@@ -2761,7 +2761,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>45.18070602416992</v>
+        <v>45.18068313598633</v>
       </c>
       <c r="C99" t="n">
         <v>75.90000152587891</v>
@@ -2790,7 +2790,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>44.12497329711914</v>
+        <v>44.12497711181641</v>
       </c>
       <c r="C100" t="n">
         <v>73.77999877929688</v>
@@ -2848,7 +2848,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>45.88925552368164</v>
+        <v>45.88925933837891</v>
       </c>
       <c r="C102" t="n">
         <v>76.73000335693359</v>
@@ -2877,7 +2877,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>44.62524032592773</v>
+        <v>44.6252326965332</v>
       </c>
       <c r="C103" t="n">
         <v>74.26000213623047</v>
@@ -2906,7 +2906,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>44.57716369628906</v>
+        <v>44.57717514038086</v>
       </c>
       <c r="C104" t="n">
         <v>74.18000030517578</v>
@@ -2935,7 +2935,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>47.7801399230957</v>
+        <v>47.78012084960938</v>
       </c>
       <c r="C105" t="n">
         <v>79.51000213623047</v>
@@ -2964,7 +2964,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>48.60784530639648</v>
+        <v>48.60784912109375</v>
       </c>
       <c r="C106" t="n">
         <v>80.52999877929688</v>
@@ -2993,7 +2993,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>47.15316009521484</v>
+        <v>47.15315628051758</v>
       </c>
       <c r="C107" t="n">
         <v>78.12000274658203</v>
@@ -3022,7 +3022,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>50.15306091308594</v>
+        <v>50.15303802490234</v>
       </c>
       <c r="C108" t="n">
         <v>83.08999633789062</v>
@@ -3051,7 +3051,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>48.02506256103516</v>
+        <v>48.02507019042969</v>
       </c>
       <c r="C109" t="n">
         <v>78.69999694824219</v>
@@ -3080,7 +3080,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>52.79096603393555</v>
+        <v>52.79095840454102</v>
       </c>
       <c r="C110" t="n">
         <v>86.51000213623047</v>
@@ -3109,7 +3109,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>52.66891479492188</v>
+        <v>52.66888427734375</v>
       </c>
       <c r="C111" t="n">
         <v>86.30999755859375</v>
@@ -3138,7 +3138,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>50.85596084594727</v>
+        <v>50.85596466064453</v>
       </c>
       <c r="C112" t="n">
         <v>82.54000091552734</v>
@@ -3167,7 +3167,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>51.46594619750977</v>
+        <v>51.46595001220703</v>
       </c>
       <c r="C113" t="n">
         <v>83.52999877929688</v>
@@ -3196,7 +3196,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.24599838256836</v>
+        <v>50.24601745605469</v>
       </c>
       <c r="C114" t="n">
         <v>81.55000305175781</v>
@@ -3225,7 +3225,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>49.96991729736328</v>
+        <v>49.96991348266602</v>
       </c>
       <c r="C115" t="n">
         <v>80.30000305175781</v>
@@ -3254,7 +3254,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>50.97179794311523</v>
+        <v>50.97180938720703</v>
       </c>
       <c r="C116" t="n">
         <v>81.91000366210938</v>
@@ -3312,7 +3312,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>49.59900665283203</v>
+        <v>49.5989990234375</v>
       </c>
       <c r="C118" t="n">
         <v>78.87000274658203</v>
@@ -3341,7 +3341,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>53.74325180053711</v>
+        <v>53.74324798583984</v>
       </c>
       <c r="C119" t="n">
         <v>85.45999908447266</v>
@@ -3370,7 +3370,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>54.02625274658203</v>
+        <v>54.0262565612793</v>
       </c>
       <c r="C120" t="n">
         <v>85.91000366210938</v>
@@ -3399,7 +3399,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>54.93244934082031</v>
+        <v>54.93245697021484</v>
       </c>
       <c r="C121" t="n">
         <v>86.44999694824219</v>
@@ -3428,7 +3428,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.77360153198242</v>
+        <v>54.77359008789062</v>
       </c>
       <c r="C122" t="n">
         <v>86.19999694824219</v>
@@ -3457,7 +3457,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>54.9642219543457</v>
+        <v>54.96422958374023</v>
       </c>
       <c r="C123" t="n">
         <v>86.5</v>
@@ -3515,7 +3515,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>55.78446197509766</v>
+        <v>55.78445434570312</v>
       </c>
       <c r="C125" t="n">
         <v>86.87999725341797</v>
@@ -3544,7 +3544,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>58.3078727722168</v>
+        <v>58.30786514282227</v>
       </c>
       <c r="C126" t="n">
         <v>90.80999755859375</v>
@@ -3573,7 +3573,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>65.74806213378906</v>
+        <v>65.74807739257812</v>
       </c>
       <c r="C127" t="n">
         <v>101.4300003051758</v>
@@ -3631,7 +3631,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>61.43097305297852</v>
+        <v>61.43099594116211</v>
       </c>
       <c r="C129" t="n">
         <v>94.76999664306641</v>
@@ -3660,7 +3660,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>61.66199111938477</v>
+        <v>61.6619758605957</v>
       </c>
       <c r="C130" t="n">
         <v>94.20999908447266</v>
@@ -3689,7 +3689,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>59.55445098876953</v>
+        <v>59.55442810058594</v>
       </c>
       <c r="C131" t="n">
         <v>90.98999786376953</v>
@@ -3718,7 +3718,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.62594223022461</v>
+        <v>54.62593841552734</v>
       </c>
       <c r="C132" t="n">
         <v>83.45999908447266</v>
@@ -3747,7 +3747,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>57.41245269775391</v>
+        <v>57.41244888305664</v>
       </c>
       <c r="C133" t="n">
         <v>86.76999664306641</v>
@@ -3776,7 +3776,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>58.11383056640625</v>
+        <v>58.11383438110352</v>
       </c>
       <c r="C134" t="n">
         <v>87.83000183105469</v>
@@ -3805,7 +3805,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>61.88529205322266</v>
+        <v>61.88530349731445</v>
       </c>
       <c r="C135" t="n">
         <v>93.52999877929688</v>
@@ -3863,7 +3863,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>63.26366806030273</v>
+        <v>63.26367568969727</v>
       </c>
       <c r="C137" t="n">
         <v>94.59999847412109</v>
@@ -3892,7 +3892,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>67.97838592529297</v>
+        <v>67.97835540771484</v>
       </c>
       <c r="C138" t="n">
         <v>101.6500015258789</v>
@@ -3921,7 +3921,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>67.62432861328125</v>
+        <v>67.62431335449219</v>
       </c>
       <c r="C139" t="n">
         <v>100.1800003051758</v>
@@ -3950,7 +3950,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>67.89431762695312</v>
+        <v>67.89432525634766</v>
       </c>
       <c r="C140" t="n">
         <v>100.5800018310547</v>
@@ -3979,7 +3979,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>73.20008087158203</v>
+        <v>73.20004272460938</v>
       </c>
       <c r="C141" t="n">
         <v>108.4400024414062</v>
@@ -4037,7 +4037,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>72.94227600097656</v>
+        <v>72.94230651855469</v>
       </c>
       <c r="C143" t="n">
         <v>107.0800018310547</v>
@@ -4066,7 +4066,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>76.97495269775391</v>
+        <v>76.97493743896484</v>
       </c>
       <c r="C144" t="n">
         <v>113</v>
@@ -4124,7 +4124,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>77.54942321777344</v>
+        <v>77.54940795898438</v>
       </c>
       <c r="C146" t="n">
         <v>112.7699966430664</v>
@@ -4153,7 +4153,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>75.68581390380859</v>
+        <v>75.68580627441406</v>
       </c>
       <c r="C147" t="n">
         <v>110.0599975585938</v>
@@ -4182,7 +4182,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>76.08918762207031</v>
+        <v>76.08917236328125</v>
       </c>
       <c r="C148" t="n">
         <v>109.6100006103516</v>
@@ -4211,7 +4211,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>70.02204132080078</v>
+        <v>70.02207183837891</v>
       </c>
       <c r="C149" t="n">
         <v>100.870002746582</v>
@@ -4240,7 +4240,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>72.29894256591797</v>
+        <v>72.29893493652344</v>
       </c>
       <c r="C150" t="n">
         <v>104.1500015258789</v>
@@ -4327,7 +4327,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>79.98844146728516</v>
+        <v>79.98843383789062</v>
       </c>
       <c r="C153" t="n">
         <v>114.0299987792969</v>
@@ -4385,7 +4385,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>76.99813079833984</v>
+        <v>76.99812316894531</v>
       </c>
       <c r="C155" t="n">
         <v>108.7399978637695</v>
@@ -4414,7 +4414,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>81.35999298095703</v>
+        <v>81.35997772216797</v>
       </c>
       <c r="C156" t="n">
         <v>114.9000015258789</v>
@@ -4443,7 +4443,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>77.67694091796875</v>
+        <v>77.67697143554688</v>
       </c>
       <c r="C157" t="n">
         <v>108.629997253418</v>
@@ -4472,7 +4472,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>83.70488739013672</v>
+        <v>83.70492553710938</v>
       </c>
       <c r="C158" t="n">
         <v>117.0599975585938</v>
@@ -4501,7 +4501,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>84.91337585449219</v>
+        <v>84.91335296630859</v>
       </c>
       <c r="C159" t="n">
         <v>118.75</v>
@@ -4588,7 +4588,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>93.80916595458984</v>
+        <v>93.80914306640625</v>
       </c>
       <c r="C162" t="n">
         <v>130.0099945068359</v>
@@ -4617,7 +4617,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>94.84432983398438</v>
+        <v>94.84435272216797</v>
       </c>
       <c r="C163" t="n">
         <v>130.3500061035156</v>
@@ -4646,7 +4646,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>96.96166229248047</v>
+        <v>96.96167755126953</v>
       </c>
       <c r="C164" t="n">
         <v>133.2599945068359</v>
@@ -4704,7 +4704,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>101.9728088378906</v>
+        <v>101.972785949707</v>
       </c>
       <c r="C166" t="n">
         <v>139.0099945068359</v>
@@ -4733,7 +4733,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>101.8114013671875</v>
+        <v>101.8113861083984</v>
       </c>
       <c r="C167" t="n">
         <v>138.7899932861328</v>
@@ -4762,7 +4762,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>98.04822540283203</v>
+        <v>98.04823303222656</v>
       </c>
       <c r="C168" t="n">
         <v>133.6600036621094</v>
@@ -4791,7 +4791,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>105.2141571044922</v>
+        <v>105.2141418457031</v>
       </c>
       <c r="C169" t="n">
         <v>142.1499938964844</v>
@@ -4820,7 +4820,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>110.9059677124023</v>
+        <v>110.9059753417969</v>
       </c>
       <c r="C170" t="n">
         <v>149.8399963378906</v>
@@ -4849,7 +4849,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>106.0579376220703</v>
+        <v>106.0579147338867</v>
       </c>
       <c r="C171" t="n">
         <v>143.2899932861328</v>
@@ -4878,7 +4878,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>107.7196731567383</v>
+        <v>107.7196884155273</v>
       </c>
       <c r="C172" t="n">
         <v>144.3999938964844</v>
@@ -4907,7 +4907,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>118.9318237304688</v>
+        <v>118.9318084716797</v>
       </c>
       <c r="C173" t="n">
         <v>159.4299926757812</v>
@@ -4936,7 +4936,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>128.4281158447266</v>
+        <v>128.4281005859375</v>
       </c>
       <c r="C174" t="n">
         <v>172.1600036621094</v>
@@ -4965,7 +4965,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>125.7064895629883</v>
+        <v>125.7064514160156</v>
       </c>
       <c r="C175" t="n">
         <v>167.3500061035156</v>
@@ -4994,7 +4994,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>127.8547592163086</v>
+        <v>127.8547439575195</v>
       </c>
       <c r="C176" t="n">
         <v>170.2100067138672</v>
@@ -5023,7 +5023,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>122.6267166137695</v>
+        <v>122.6267013549805</v>
       </c>
       <c r="C177" t="n">
         <v>163.25</v>
@@ -5052,7 +5052,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>126.0215148925781</v>
+        <v>126.0215377807617</v>
       </c>
       <c r="C178" t="n">
         <v>166.5</v>
@@ -5081,7 +5081,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>118.2256011962891</v>
+        <v>118.2256164550781</v>
       </c>
       <c r="C179" t="n">
         <v>156.1999969482422</v>
@@ -5110,7 +5110,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>126.8314056396484</v>
+        <v>126.8313827514648</v>
       </c>
       <c r="C180" t="n">
         <v>167.5700073242188</v>
@@ -5139,7 +5139,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>121.5136260986328</v>
+        <v>121.5136566162109</v>
       </c>
       <c r="C181" t="n">
         <v>159.1900024414062</v>
@@ -5168,7 +5168,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.5670852661133</v>
+        <v>121.5670928955078</v>
       </c>
       <c r="C182" t="n">
         <v>159.2599945068359</v>
@@ -5197,7 +5197,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>118.8878021240234</v>
+        <v>118.887809753418</v>
       </c>
       <c r="C183" t="n">
         <v>155.75</v>
@@ -5226,7 +5226,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.5227661132812</v>
+        <v>132.5228118896484</v>
       </c>
       <c r="C184" t="n">
         <v>172.1300048828125</v>
@@ -5284,7 +5284,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>145.8959350585938</v>
+        <v>145.8959197998047</v>
       </c>
       <c r="C186" t="n">
         <v>189.5</v>
@@ -5313,7 +5313,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>151.2117156982422</v>
+        <v>151.2117462158203</v>
       </c>
       <c r="C187" t="n">
         <v>195.1000061035156</v>
@@ -5342,7 +5342,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>149.6538543701172</v>
+        <v>149.6538696289062</v>
       </c>
       <c r="C188" t="n">
         <v>193.0899963378906</v>
@@ -5400,7 +5400,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>135.2790374755859</v>
+        <v>135.2790069580078</v>
       </c>
       <c r="C190" t="n">
         <v>173.3200073242188</v>
@@ -5429,7 +5429,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>140.7269897460938</v>
+        <v>140.7270202636719</v>
       </c>
       <c r="C191" t="n">
         <v>180.3000030517578</v>
@@ -5458,7 +5458,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>141.7807006835938</v>
+        <v>141.7807312011719</v>
       </c>
       <c r="C192" t="n">
         <v>181.6499938964844</v>
@@ -5487,7 +5487,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>164.1396636962891</v>
+        <v>164.1396484375</v>
       </c>
       <c r="C193" t="n">
         <v>208.7400054931641</v>
@@ -5516,7 +5516,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>143.5140686035156</v>
+        <v>143.5140380859375</v>
       </c>
       <c r="C194" t="n">
         <v>182.5099945068359</v>
@@ -5545,7 +5545,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>130.9955596923828</v>
+        <v>130.99560546875</v>
       </c>
       <c r="C195" t="n">
         <v>166.5899963378906</v>
@@ -5574,7 +5574,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>146.3969573974609</v>
+        <v>146.3969421386719</v>
       </c>
       <c r="C196" t="n">
         <v>184.6000061035156</v>
@@ -5603,7 +5603,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>146.8807067871094</v>
+        <v>146.8806915283203</v>
       </c>
       <c r="C197" t="n">
         <v>185.2100067138672</v>
@@ -5632,7 +5632,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>150.4018096923828</v>
+        <v>150.40185546875</v>
       </c>
       <c r="C198" t="n">
         <v>189.6499938964844</v>
@@ -5661,7 +5661,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>134.7264404296875</v>
+        <v>134.7264862060547</v>
       </c>
       <c r="C199" t="n">
         <v>168.3800048828125</v>
@@ -5719,7 +5719,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>136.6867828369141</v>
+        <v>136.6867523193359</v>
       </c>
       <c r="C201" t="n">
         <v>170.8300018310547</v>
@@ -5748,7 +5748,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>116.6733627319336</v>
+        <v>116.6733474731445</v>
       </c>
       <c r="C202" t="n">
         <v>144.5500030517578</v>
@@ -5777,7 +5777,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>107.5606307983398</v>
+        <v>107.5606384277344</v>
       </c>
       <c r="C203" t="n">
         <v>133.2599945068359</v>
@@ -5806,7 +5806,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>114.1550140380859</v>
+        <v>114.155029296875</v>
       </c>
       <c r="C204" t="n">
         <v>141.4299926757812</v>
@@ -5835,7 +5835,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>110.6764450073242</v>
+        <v>110.6764373779297</v>
       </c>
       <c r="C205" t="n">
         <v>135.6399993896484</v>
@@ -5864,7 +5864,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>120.8514175415039</v>
+        <v>120.8514404296875</v>
       </c>
       <c r="C206" t="n">
         <v>148.1100006103516</v>
@@ -5922,7 +5922,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>110.5324478149414</v>
+        <v>110.5324401855469</v>
       </c>
       <c r="C208" t="n">
         <v>133.8399963378906</v>
@@ -5980,7 +5980,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>93.49506378173828</v>
+        <v>93.49505615234375</v>
       </c>
       <c r="C210" t="n">
         <v>113.2099990844727</v>
@@ -6009,7 +6009,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>95.38930511474609</v>
+        <v>95.38932800292969</v>
       </c>
       <c r="C211" t="n">
         <v>113.9400024414062</v>
@@ -6038,7 +6038,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>90.65919494628906</v>
+        <v>90.65922546386719</v>
       </c>
       <c r="C212" t="n">
         <v>108.2900009155273</v>
@@ -6067,7 +6067,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>84.13749694824219</v>
+        <v>84.13750457763672</v>
       </c>
       <c r="C213" t="n">
         <v>100.5</v>
@@ -6096,7 +6096,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>78.30416870117188</v>
+        <v>78.30417633056641</v>
       </c>
       <c r="C214" t="n">
         <v>92.02999877929688</v>
@@ -6125,7 +6125,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>79.11248016357422</v>
+        <v>79.11248779296875</v>
       </c>
       <c r="C215" t="n">
         <v>92.98000335693359</v>
@@ -6183,7 +6183,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>99.34150695800781</v>
+        <v>99.34149169921875</v>
       </c>
       <c r="C217" t="n">
         <v>115.1900024414062</v>
@@ -6212,7 +6212,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>93.35633087158203</v>
+        <v>93.35634613037109</v>
       </c>
       <c r="C218" t="n">
         <v>108.25</v>
@@ -6241,7 +6241,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>94.81380462646484</v>
+        <v>94.81381225585938</v>
       </c>
       <c r="C219" t="n">
         <v>109.9400024414062</v>
@@ -6299,7 +6299,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>82.04351043701172</v>
+        <v>82.04350280761719</v>
       </c>
       <c r="C221" t="n">
         <v>93.77999877929688</v>
@@ -6328,7 +6328,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>89.67219543457031</v>
+        <v>89.67220306396484</v>
       </c>
       <c r="C222" t="n">
         <v>102.5</v>
@@ -6386,7 +6386,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>97.83733367919922</v>
+        <v>97.83734130859375</v>
       </c>
       <c r="C224" t="n">
         <v>110.0800018310547</v>
@@ -6415,7 +6415,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56157684326172</v>
+        <v>99.56156921386719</v>
       </c>
       <c r="C225" t="n">
         <v>112.0199966430664</v>
@@ -6444,7 +6444,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>106.840705871582</v>
+        <v>106.8406982421875</v>
       </c>
       <c r="C226" t="n">
         <v>118.629997253418</v>
@@ -6473,7 +6473,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>96.80777740478516</v>
+        <v>96.80778503417969</v>
       </c>
       <c r="C227" t="n">
         <v>107.4899978637695</v>
@@ -6531,7 +6531,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>83.05640411376953</v>
+        <v>83.05641174316406</v>
       </c>
       <c r="C229" t="n">
         <v>90.76000213623047</v>
@@ -6560,7 +6560,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>81.7020263671875</v>
+        <v>81.70203399658203</v>
       </c>
       <c r="C230" t="n">
         <v>89.27999877929688</v>
@@ -6618,7 +6618,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>96.97917175292969</v>
+        <v>96.97918701171875</v>
       </c>
       <c r="C232" t="n">
         <v>104.2300033569336</v>
@@ -6645,7 +6645,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>98.40274047851562</v>
+        <v>98.40275573730469</v>
       </c>
       <c r="C233" t="n">
         <v>105.7600021362305</v>
@@ -6672,7 +6672,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>93.36909484863281</v>
+        <v>93.36908721923828</v>
       </c>
       <c r="C234" t="n">
         <v>100.3499984741211</v>
@@ -6753,7 +6753,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>93.23404693603516</v>
+        <v>93.23405456542969</v>
       </c>
       <c r="C237" t="n">
         <v>99.13999938964844</v>
@@ -6780,7 +6780,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>91.76451873779297</v>
+        <v>91.76450347900391</v>
       </c>
       <c r="C238" t="n">
         <v>96.48999786376953</v>
@@ -6807,7 +6807,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>85.80158233642578</v>
+        <v>85.80158996582031</v>
       </c>
       <c r="C239" t="n">
         <v>90.22000122070312</v>
@@ -6834,7 +6834,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>86.80966949462891</v>
+        <v>86.80966186523438</v>
       </c>
       <c r="C240" t="n">
         <v>91.27999877929688</v>
@@ -6973,7 +6973,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>86.49826812744141</v>
+        <v>86.49827575683594</v>
       </c>
       <c r="C245" t="n">
         <v>88.77999877929688</v>
@@ -7002,7 +7002,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>89.14836883544922</v>
+        <v>89.14836120605469</v>
       </c>
       <c r="C246" t="n">
         <v>91.5</v>
